--- a/research/results/121225/summary_eval.xlsx
+++ b/research/results/121225/summary_eval.xlsx
@@ -1,40 +1,345 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Harshit Nigam\Desktop\Coding\Table Diversification\research\results\121225\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B33E7FC5-DA36-450C-B6C0-E26757B020C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="verdict" sheetId="1" r:id="rId1"/>
+    <sheet name="error_analysis" sheetId="2" r:id="rId2"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="81">
+  <si>
+    <t>query_index</t>
+  </si>
+  <si>
+    <t>query</t>
+  </si>
+  <si>
+    <t>data_file</t>
+  </si>
+  <si>
+    <t>original</t>
+  </si>
+  <si>
+    <t>hierarchical_column_header__diversified</t>
+  </si>
+  <si>
+    <t>transpose_table__diversified</t>
+  </si>
+  <si>
+    <t>single_hierarchical_row_header__diversified</t>
+  </si>
+  <si>
+    <t>merge_similar_columns__diversified</t>
+  </si>
+  <si>
+    <t>hierarchical_column_header__disturbed</t>
+  </si>
+  <si>
+    <t>merge_similar_columns__disturbed</t>
+  </si>
+  <si>
+    <t>single_hierarchical_row_header__disturbed</t>
+  </si>
+  <si>
+    <t>transpose_table__disturbed</t>
+  </si>
+  <si>
+    <t>Retail_Sales_Orders_original_0</t>
+  </si>
+  <si>
+    <t>Looking at all the sales orders, what is the total revenue (NetAmount) generated in each region, and can you list them in descending order of revenue?</t>
+  </si>
+  <si>
+    <t>dev_test/Diversification/Self Created Dataset/Manual Created Dataset/Normal Diversifications/Retail_Sales_Orders/Retail_Sales_Orders_original.xlsx</t>
+  </si>
+  <si>
+    <t>Retail_Sales_Orders_original_1</t>
+  </si>
+  <si>
+    <t>Which product sold the most units overall across all orders? (mention only the product name)</t>
+  </si>
+  <si>
+    <t>Retail_Sales_Orders_original_2</t>
+  </si>
+  <si>
+    <t>What is the average discount rate (rounded to 3 decimals) applied to orders shipped via Express compared to those shipped via Standard?</t>
+  </si>
+  <si>
+    <t>Retail_Sales_Orders_original_3</t>
+  </si>
+  <si>
+    <t>What percentage of orders were delivered within two days of the order date?</t>
+  </si>
+  <si>
+    <t>HR_Timesheets_original_0</t>
+  </si>
+  <si>
+    <t>For all billable entries, what is the total revenue generated grouped by project?</t>
+  </si>
+  <si>
+    <t>dev_test/Diversification/Self Created Dataset/Manual Created Dataset/Normal Diversifications/HR_Timesheets/HR_Timesheets_original.xlsx</t>
+  </si>
+  <si>
+    <t>HR_Timesheets_original_1</t>
+  </si>
+  <si>
+    <t>How many employees did overtime?</t>
+  </si>
+  <si>
+    <t>HR_Timesheets_original_2</t>
+  </si>
+  <si>
+    <t>What is the average number of hours worked for employees working remotely compared to those onsite?</t>
+  </si>
+  <si>
+    <t>Logistics_Shipments_original_0</t>
+  </si>
+  <si>
+    <t>What is the average number of transit days for each carrier for Standard priority level?</t>
+  </si>
+  <si>
+    <t>dev_test/Diversification/Self Created Dataset/Manual Created Dataset/Normal Diversifications/Logistics_Shipments/Logistics_Shipments_original.xlsx</t>
+  </si>
+  <si>
+    <t>Logistics_Shipments_original_1</t>
+  </si>
+  <si>
+    <t>Which three destinations received the highest total shipment weight?</t>
+  </si>
+  <si>
+    <t>Logistics_Shipments_original_2</t>
+  </si>
+  <si>
+    <t>What percentage of shipments met the on-time delivery rule (Priority ≤ 4 days, Standard ≤ 6 days), rounded to nearest integer?</t>
+  </si>
+  <si>
+    <t>Clinic_Visits_original_0</t>
+  </si>
+  <si>
+    <t>What is the median systolic blood pressure recorded for patients grouped by their medical condition?</t>
+  </si>
+  <si>
+    <t>dev_test/Diversification/Self Created Dataset/Manual Created Dataset/Normal Diversifications/Clinic_Visits/Clinic_Visits_original.xlsx</t>
+  </si>
+  <si>
+    <t>Clinic_Visits_original_1</t>
+  </si>
+  <si>
+    <t>For each doctor, what proportion of their visits required a follow-up?</t>
+  </si>
+  <si>
+    <t>Clinic_Visits_original_2</t>
+  </si>
+  <si>
+    <t>What is the average consultation fee for females grouped by condition?</t>
+  </si>
+  <si>
+    <t>Personal_Finance_Transactions_original_0</t>
+  </si>
+  <si>
+    <t>What is the total spending for each category in the month of June?</t>
+  </si>
+  <si>
+    <t>dev_test/Diversification/Self Created Dataset/Manual Created Dataset/Normal Diversifications/Personal_Finance_Transactions/Personal_Finance_Transactions_original.xlsx</t>
+  </si>
+  <si>
+    <t>Personal_Finance_Transactions_original_1</t>
+  </si>
+  <si>
+    <t>Which payment method (mention only name) earned the highest total cashback?</t>
+  </si>
+  <si>
+    <t>Personal_Finance_Transactions_original_2</t>
+  </si>
+  <si>
+    <t>What percent of total spending was on recurring expenses?</t>
+  </si>
+  <si>
+    <t>University_Grades_original_0</t>
+  </si>
+  <si>
+    <t>What is the average total score for each course with a 100% pass rate?</t>
+  </si>
+  <si>
+    <t>dev_test/Diversification/Self Created Dataset/Manual Created Dataset/Normal Diversifications/University_Grades/University_Grades_original.xlsx</t>
+  </si>
+  <si>
+    <t>University_Grades_original_1</t>
+  </si>
+  <si>
+    <t>How many students received grade A?</t>
+  </si>
+  <si>
+    <t>University_Grades_original_2</t>
+  </si>
+  <si>
+    <t>Which professor (only name) achieved the highest average project score?</t>
+  </si>
+  <si>
+    <t>University_Grades_original_3</t>
+  </si>
+  <si>
+    <t>Among all students, which student achieved the highest overall score, and what was their total marks along with the corresponding letter grade? Mention as a dictionary with keys 'StudentID', 'Marks', and 'Grade'.</t>
+  </si>
+  <si>
+    <t>Wrong Assumption in Code</t>
+  </si>
+  <si>
+    <t>Incomplete Process</t>
+  </si>
+  <si>
+    <t>Pandas can't understand merged columns</t>
+  </si>
+  <si>
+    <t>Case Mismatch but Correct Answer</t>
+  </si>
+  <si>
+    <t>Diversification Error</t>
+  </si>
+  <si>
+    <t>Ground Truth is Wrong</t>
+  </si>
+  <si>
+    <t>Error in Code</t>
+  </si>
+  <si>
+    <t>Wrong Assumption in Code*</t>
+  </si>
+  <si>
+    <t>Error in Code*</t>
+  </si>
+  <si>
+    <t>Disturbance Error</t>
+  </si>
+  <si>
+    <t>Wrong Ground Truth</t>
+  </si>
+  <si>
+    <t>Wrong Output</t>
+  </si>
+  <si>
+    <t>Wrong Output not due to fault of LLM</t>
+  </si>
+  <si>
+    <t>LLM Output is Correct but eval marked wrong</t>
+  </si>
+  <si>
+    <t>Wrong output caused due to disturbance</t>
+  </si>
+  <si>
+    <t>Wrong output caused due to diversification</t>
+  </si>
+  <si>
+    <t>Color Key</t>
+  </si>
+  <si>
+    <t>LLM was on right track but didn't continue</t>
+  </si>
+  <si>
+    <t>15/20</t>
+  </si>
+  <si>
+    <t>12/20</t>
+  </si>
+  <si>
+    <t>16/20</t>
+  </si>
+  <si>
+    <t>14/20</t>
+  </si>
+  <si>
+    <t>9/20</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b val="1"/>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="9">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF0070C0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC00000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B0F0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -46,93 +351,79 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+  <cellXfs count="20">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -420,91 +711,57 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:L21"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>query_index</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>query</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>data_file</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>original</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>hierarchical_column_header__diversified</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>transpose_table__diversified</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>single_hierarchical_row_header__diversified</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>merge_similar_columns__diversified</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>hierarchical_column_header__disturbed</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>merge_similar_columns__disturbed</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>single_hierarchical_row_header__disturbed</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>transpose_table__disturbed</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Retail_Sales_Orders_original_0</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Looking at all the sales orders, what is the total revenue (NetAmount) generated in each region, and can you list them in descending order of revenue?</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>dev_test/Diversification/Self Created Dataset/Manual Created Dataset/Normal Diversifications/Retail_Sales_Orders/Retail_Sales_Orders_original.xlsx</t>
-        </is>
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" t="s">
+        <v>14</v>
       </c>
       <c r="D2" t="b">
         <v>1</v>
@@ -534,21 +791,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Retail_Sales_Orders_original_1</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Which product sold the most units overall across all orders? (mention only the product name)</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>dev_test/Diversification/Self Created Dataset/Manual Created Dataset/Normal Diversifications/Retail_Sales_Orders/Retail_Sales_Orders_original.xlsx</t>
-        </is>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" t="s">
+        <v>14</v>
       </c>
       <c r="D3" t="b">
         <v>0</v>
@@ -578,21 +829,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Retail_Sales_Orders_original_2</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>What is the average discount rate (rounded to 3 decimals) applied to orders shipped via Express compared to those shipped via Standard?</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>dev_test/Diversification/Self Created Dataset/Manual Created Dataset/Normal Diversifications/Retail_Sales_Orders/Retail_Sales_Orders_original.xlsx</t>
-        </is>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" t="s">
+        <v>14</v>
       </c>
       <c r="D4" t="b">
         <v>1</v>
@@ -622,21 +867,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Retail_Sales_Orders_original_3</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>What percentage of orders were delivered within two days of the order date?</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>dev_test/Diversification/Self Created Dataset/Manual Created Dataset/Normal Diversifications/Retail_Sales_Orders/Retail_Sales_Orders_original.xlsx</t>
-        </is>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C5" t="s">
+        <v>14</v>
       </c>
       <c r="D5" t="b">
         <v>1</v>
@@ -666,21 +905,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>HR_Timesheets_original_0</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>For all billable entries, what is the total revenue generated grouped by project?</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>dev_test/Diversification/Self Created Dataset/Manual Created Dataset/Normal Diversifications/HR_Timesheets/HR_Timesheets_original.xlsx</t>
-        </is>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>21</v>
+      </c>
+      <c r="B6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6" t="s">
+        <v>23</v>
       </c>
       <c r="D6" t="b">
         <v>1</v>
@@ -710,21 +943,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>HR_Timesheets_original_1</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>How many employees did overtime?</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>dev_test/Diversification/Self Created Dataset/Manual Created Dataset/Normal Diversifications/HR_Timesheets/HR_Timesheets_original.xlsx</t>
-        </is>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C7" t="s">
+        <v>23</v>
       </c>
       <c r="D7" t="b">
         <v>1</v>
@@ -754,21 +981,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>HR_Timesheets_original_2</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>What is the average number of hours worked for employees working remotely compared to those onsite?</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>dev_test/Diversification/Self Created Dataset/Manual Created Dataset/Normal Diversifications/HR_Timesheets/HR_Timesheets_original.xlsx</t>
-        </is>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>26</v>
+      </c>
+      <c r="B8" t="s">
+        <v>27</v>
+      </c>
+      <c r="C8" t="s">
+        <v>23</v>
       </c>
       <c r="D8" t="b">
         <v>1</v>
@@ -798,21 +1019,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Logistics_Shipments_original_0</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>What is the average number of transit days for each carrier for Standard priority level?</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>dev_test/Diversification/Self Created Dataset/Manual Created Dataset/Normal Diversifications/Logistics_Shipments/Logistics_Shipments_original.xlsx</t>
-        </is>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>28</v>
+      </c>
+      <c r="B9" t="s">
+        <v>29</v>
+      </c>
+      <c r="C9" t="s">
+        <v>30</v>
       </c>
       <c r="D9" t="b">
         <v>1</v>
@@ -842,21 +1057,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Logistics_Shipments_original_1</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Which three destinations received the highest total shipment weight?</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>dev_test/Diversification/Self Created Dataset/Manual Created Dataset/Normal Diversifications/Logistics_Shipments/Logistics_Shipments_original.xlsx</t>
-        </is>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>31</v>
+      </c>
+      <c r="B10" t="s">
+        <v>32</v>
+      </c>
+      <c r="C10" t="s">
+        <v>30</v>
       </c>
       <c r="D10" t="b">
         <v>1</v>
@@ -886,21 +1095,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Logistics_Shipments_original_2</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>What percentage of shipments met the on-time delivery rule (Priority ≤ 4 days, Standard ≤ 6 days), rounded to nearest integer?</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>dev_test/Diversification/Self Created Dataset/Manual Created Dataset/Normal Diversifications/Logistics_Shipments/Logistics_Shipments_original.xlsx</t>
-        </is>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>33</v>
+      </c>
+      <c r="B11" t="s">
+        <v>34</v>
+      </c>
+      <c r="C11" t="s">
+        <v>30</v>
       </c>
       <c r="D11" t="b">
         <v>1</v>
@@ -930,21 +1133,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Clinic_Visits_original_0</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>What is the median systolic blood pressure recorded for patients grouped by their medical condition?</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>dev_test/Diversification/Self Created Dataset/Manual Created Dataset/Normal Diversifications/Clinic_Visits/Clinic_Visits_original.xlsx</t>
-        </is>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>35</v>
+      </c>
+      <c r="B12" t="s">
+        <v>36</v>
+      </c>
+      <c r="C12" t="s">
+        <v>37</v>
       </c>
       <c r="D12" t="b">
         <v>1</v>
@@ -974,21 +1171,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Clinic_Visits_original_1</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>For each doctor, what proportion of their visits required a follow-up?</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>dev_test/Diversification/Self Created Dataset/Manual Created Dataset/Normal Diversifications/Clinic_Visits/Clinic_Visits_original.xlsx</t>
-        </is>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>38</v>
+      </c>
+      <c r="B13" t="s">
+        <v>39</v>
+      </c>
+      <c r="C13" t="s">
+        <v>37</v>
       </c>
       <c r="D13" t="b">
         <v>1</v>
@@ -1018,21 +1209,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Clinic_Visits_original_2</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>What is the average consultation fee for females grouped by condition?</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>dev_test/Diversification/Self Created Dataset/Manual Created Dataset/Normal Diversifications/Clinic_Visits/Clinic_Visits_original.xlsx</t>
-        </is>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>40</v>
+      </c>
+      <c r="B14" t="s">
+        <v>41</v>
+      </c>
+      <c r="C14" t="s">
+        <v>37</v>
       </c>
       <c r="D14" t="b">
         <v>0</v>
@@ -1062,21 +1247,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Personal_Finance_Transactions_original_0</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>What is the total spending for each category in the month of June?</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>dev_test/Diversification/Self Created Dataset/Manual Created Dataset/Normal Diversifications/Personal_Finance_Transactions/Personal_Finance_Transactions_original.xlsx</t>
-        </is>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>42</v>
+      </c>
+      <c r="B15" t="s">
+        <v>43</v>
+      </c>
+      <c r="C15" t="s">
+        <v>44</v>
       </c>
       <c r="D15" t="b">
         <v>0</v>
@@ -1106,21 +1285,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Personal_Finance_Transactions_original_1</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Which payment method (mention only name) earned the highest total cashback?</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>dev_test/Diversification/Self Created Dataset/Manual Created Dataset/Normal Diversifications/Personal_Finance_Transactions/Personal_Finance_Transactions_original.xlsx</t>
-        </is>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>45</v>
+      </c>
+      <c r="B16" t="s">
+        <v>46</v>
+      </c>
+      <c r="C16" t="s">
+        <v>44</v>
       </c>
       <c r="D16" t="b">
         <v>1</v>
@@ -1150,21 +1323,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Personal_Finance_Transactions_original_2</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>What percent of total spending was on recurring expenses?</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>dev_test/Diversification/Self Created Dataset/Manual Created Dataset/Normal Diversifications/Personal_Finance_Transactions/Personal_Finance_Transactions_original.xlsx</t>
-        </is>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>47</v>
+      </c>
+      <c r="B17" t="s">
+        <v>48</v>
+      </c>
+      <c r="C17" t="s">
+        <v>44</v>
       </c>
       <c r="D17" t="b">
         <v>0</v>
@@ -1194,21 +1361,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>University_Grades_original_0</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>What is the average total score for each course with a 100% pass rate?</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>dev_test/Diversification/Self Created Dataset/Manual Created Dataset/Normal Diversifications/University_Grades/University_Grades_original.xlsx</t>
-        </is>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>49</v>
+      </c>
+      <c r="B18" t="s">
+        <v>50</v>
+      </c>
+      <c r="C18" t="s">
+        <v>51</v>
       </c>
       <c r="D18" t="b">
         <v>0</v>
@@ -1238,21 +1399,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>University_Grades_original_1</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>How many students received grade A?</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>dev_test/Diversification/Self Created Dataset/Manual Created Dataset/Normal Diversifications/University_Grades/University_Grades_original.xlsx</t>
-        </is>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>52</v>
+      </c>
+      <c r="B19" t="s">
+        <v>53</v>
+      </c>
+      <c r="C19" t="s">
+        <v>51</v>
       </c>
       <c r="D19" t="b">
         <v>1</v>
@@ -1282,21 +1437,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>University_Grades_original_2</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Which professor (only name) achieved the highest average project score?</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>dev_test/Diversification/Self Created Dataset/Manual Created Dataset/Normal Diversifications/University_Grades/University_Grades_original.xlsx</t>
-        </is>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>54</v>
+      </c>
+      <c r="B20" t="s">
+        <v>55</v>
+      </c>
+      <c r="C20" t="s">
+        <v>51</v>
       </c>
       <c r="D20" t="b">
         <v>1</v>
@@ -1326,21 +1475,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>University_Grades_original_3</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Among all students, which student achieved the highest overall score, and what was their total marks along with the corresponding letter grade? Mention as a dictionary with keys 'StudentID', 'Marks', and 'Grade'.</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>dev_test/Diversification/Self Created Dataset/Manual Created Dataset/Normal Diversifications/University_Grades/University_Grades_original.xlsx</t>
-        </is>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>56</v>
+      </c>
+      <c r="B21" t="s">
+        <v>57</v>
+      </c>
+      <c r="C21" t="s">
+        <v>51</v>
       </c>
       <c r="D21" t="b">
         <v>1</v>
@@ -1373,4 +1516,919 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EA749501-AD3C-477A-A38E-0888BB21F4C2}">
+  <dimension ref="A1:P22"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="5" max="5" width="9.5703125" customWidth="1"/>
+    <col min="6" max="6" width="9.85546875" customWidth="1"/>
+    <col min="7" max="7" width="9.5703125" customWidth="1"/>
+    <col min="8" max="8" width="10" customWidth="1"/>
+    <col min="9" max="9" width="10.5703125" customWidth="1"/>
+    <col min="10" max="11" width="11.140625" customWidth="1"/>
+    <col min="12" max="12" width="10.85546875" customWidth="1"/>
+    <col min="15" max="15" width="10.42578125" customWidth="1"/>
+    <col min="16" max="16" width="23" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2" t="b">
+        <v>1</v>
+      </c>
+      <c r="E2" t="b">
+        <v>1</v>
+      </c>
+      <c r="F2" t="b">
+        <v>1</v>
+      </c>
+      <c r="G2" t="b">
+        <v>1</v>
+      </c>
+      <c r="H2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I2" t="b">
+        <v>1</v>
+      </c>
+      <c r="J2" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="K2" t="b">
+        <v>1</v>
+      </c>
+      <c r="L2" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="O2" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="P2" s="10"/>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="F3" t="b">
+        <v>1</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="H3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I3" t="b">
+        <v>1</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="K3" t="b">
+        <v>1</v>
+      </c>
+      <c r="L3" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="O3" s="11"/>
+      <c r="P3" s="12" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" t="b">
+        <v>1</v>
+      </c>
+      <c r="E4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="H4" t="b">
+        <v>1</v>
+      </c>
+      <c r="I4" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="J4" t="b">
+        <v>1</v>
+      </c>
+      <c r="K4" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="L4" t="b">
+        <v>1</v>
+      </c>
+      <c r="O4" s="11"/>
+      <c r="P4" s="12"/>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D5" t="b">
+        <v>1</v>
+      </c>
+      <c r="E5" t="b">
+        <v>1</v>
+      </c>
+      <c r="F5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G5" t="b">
+        <v>1</v>
+      </c>
+      <c r="H5" t="b">
+        <v>1</v>
+      </c>
+      <c r="I5" t="b">
+        <v>1</v>
+      </c>
+      <c r="J5" t="b">
+        <v>1</v>
+      </c>
+      <c r="K5" t="b">
+        <v>1</v>
+      </c>
+      <c r="L5" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="O5" s="13"/>
+      <c r="P5" s="12" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>21</v>
+      </c>
+      <c r="B6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6" t="s">
+        <v>23</v>
+      </c>
+      <c r="D6" t="b">
+        <v>1</v>
+      </c>
+      <c r="E6" t="b">
+        <v>1</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="H6" t="b">
+        <v>1</v>
+      </c>
+      <c r="I6" t="b">
+        <v>1</v>
+      </c>
+      <c r="J6" t="b">
+        <v>1</v>
+      </c>
+      <c r="K6" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="L6" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="O6" s="13"/>
+      <c r="P6" s="12"/>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D7" t="b">
+        <v>1</v>
+      </c>
+      <c r="E7" t="b">
+        <v>1</v>
+      </c>
+      <c r="F7" t="b">
+        <v>1</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="H7" t="b">
+        <v>1</v>
+      </c>
+      <c r="I7" t="b">
+        <v>1</v>
+      </c>
+      <c r="J7" t="b">
+        <v>1</v>
+      </c>
+      <c r="K7" t="b">
+        <v>1</v>
+      </c>
+      <c r="L7" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="O7" s="14"/>
+      <c r="P7" s="12" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>26</v>
+      </c>
+      <c r="B8" t="s">
+        <v>27</v>
+      </c>
+      <c r="C8" t="s">
+        <v>23</v>
+      </c>
+      <c r="D8" t="b">
+        <v>1</v>
+      </c>
+      <c r="E8" t="b">
+        <v>1</v>
+      </c>
+      <c r="F8" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="G8" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="H8" t="b">
+        <v>1</v>
+      </c>
+      <c r="I8" t="b">
+        <v>1</v>
+      </c>
+      <c r="J8" t="b">
+        <v>1</v>
+      </c>
+      <c r="K8" t="b">
+        <v>1</v>
+      </c>
+      <c r="L8" t="b">
+        <v>1</v>
+      </c>
+      <c r="O8" s="14"/>
+      <c r="P8" s="12"/>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>28</v>
+      </c>
+      <c r="B9" t="s">
+        <v>29</v>
+      </c>
+      <c r="C9" t="s">
+        <v>30</v>
+      </c>
+      <c r="D9" t="b">
+        <v>1</v>
+      </c>
+      <c r="E9" t="b">
+        <v>1</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="G9" t="b">
+        <v>1</v>
+      </c>
+      <c r="H9" t="b">
+        <v>1</v>
+      </c>
+      <c r="I9" t="b">
+        <v>1</v>
+      </c>
+      <c r="J9" t="b">
+        <v>1</v>
+      </c>
+      <c r="K9" t="b">
+        <v>1</v>
+      </c>
+      <c r="L9" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="O9" s="15"/>
+      <c r="P9" s="12" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>31</v>
+      </c>
+      <c r="B10" t="s">
+        <v>32</v>
+      </c>
+      <c r="C10" t="s">
+        <v>30</v>
+      </c>
+      <c r="D10" t="b">
+        <v>1</v>
+      </c>
+      <c r="E10" t="b">
+        <v>1</v>
+      </c>
+      <c r="F10" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="G10" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="H10" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="I10" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="J10" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="K10" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="L10" t="b">
+        <v>1</v>
+      </c>
+      <c r="O10" s="15"/>
+      <c r="P10" s="12"/>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>33</v>
+      </c>
+      <c r="B11" t="s">
+        <v>34</v>
+      </c>
+      <c r="C11" t="s">
+        <v>30</v>
+      </c>
+      <c r="D11" t="b">
+        <v>1</v>
+      </c>
+      <c r="E11" t="b">
+        <v>1</v>
+      </c>
+      <c r="F11" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="G11" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="H11" t="b">
+        <v>1</v>
+      </c>
+      <c r="I11" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="J11" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="K11" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="L11" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="O11" s="16"/>
+      <c r="P11" s="12" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>35</v>
+      </c>
+      <c r="B12" t="s">
+        <v>36</v>
+      </c>
+      <c r="C12" t="s">
+        <v>37</v>
+      </c>
+      <c r="D12" t="b">
+        <v>1</v>
+      </c>
+      <c r="E12" t="b">
+        <v>1</v>
+      </c>
+      <c r="F12" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="G12" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="H12" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="I12" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="J12" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="K12" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="L12" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="O12" s="16"/>
+      <c r="P12" s="12"/>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>38</v>
+      </c>
+      <c r="B13" t="s">
+        <v>39</v>
+      </c>
+      <c r="C13" t="s">
+        <v>37</v>
+      </c>
+      <c r="D13" t="b">
+        <v>1</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="F13" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="G13" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="H13" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="I13" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="J13" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="K13" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="L13" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="O13" s="17"/>
+      <c r="P13" s="12" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>40</v>
+      </c>
+      <c r="B14" t="s">
+        <v>41</v>
+      </c>
+      <c r="C14" t="s">
+        <v>37</v>
+      </c>
+      <c r="D14" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="F14" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="G14" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="J14" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="K14" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="L14" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="O14" s="17"/>
+      <c r="P14" s="12"/>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>42</v>
+      </c>
+      <c r="B15" t="s">
+        <v>43</v>
+      </c>
+      <c r="C15" t="s">
+        <v>44</v>
+      </c>
+      <c r="D15" t="b">
+        <v>0</v>
+      </c>
+      <c r="E15" t="b">
+        <v>1</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="G15" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="H15" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="I15" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="J15" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="K15" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="L15" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="O15" s="18"/>
+      <c r="P15" s="12" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>45</v>
+      </c>
+      <c r="B16" t="s">
+        <v>46</v>
+      </c>
+      <c r="C16" t="s">
+        <v>44</v>
+      </c>
+      <c r="D16" t="b">
+        <v>1</v>
+      </c>
+      <c r="E16" t="b">
+        <v>1</v>
+      </c>
+      <c r="F16" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="G16" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="I16" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="J16" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="K16" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="L16" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="O16" s="18"/>
+      <c r="P16" s="12"/>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>47</v>
+      </c>
+      <c r="B17" t="s">
+        <v>48</v>
+      </c>
+      <c r="C17" t="s">
+        <v>44</v>
+      </c>
+      <c r="D17" t="b">
+        <v>0</v>
+      </c>
+      <c r="E17" t="b">
+        <v>1</v>
+      </c>
+      <c r="F17" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="G17" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="I17" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="J17" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="K17" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="L17" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>49</v>
+      </c>
+      <c r="B18" t="s">
+        <v>50</v>
+      </c>
+      <c r="C18" t="s">
+        <v>51</v>
+      </c>
+      <c r="D18" t="b">
+        <v>0</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="G18" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="H18" t="b">
+        <v>1</v>
+      </c>
+      <c r="I18" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="J18" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="K18" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="L18" s="2" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>52</v>
+      </c>
+      <c r="B19" t="s">
+        <v>53</v>
+      </c>
+      <c r="C19" t="s">
+        <v>51</v>
+      </c>
+      <c r="D19" t="b">
+        <v>1</v>
+      </c>
+      <c r="E19" t="b">
+        <v>1</v>
+      </c>
+      <c r="F19" t="b">
+        <v>1</v>
+      </c>
+      <c r="G19" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="H19" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="I19" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="J19" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="K19" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="L19" s="6" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>54</v>
+      </c>
+      <c r="B20" t="s">
+        <v>55</v>
+      </c>
+      <c r="C20" t="s">
+        <v>51</v>
+      </c>
+      <c r="D20" t="b">
+        <v>1</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="G20" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="H20" t="b">
+        <v>1</v>
+      </c>
+      <c r="I20" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="J20" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="K20" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="L20" s="6" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>56</v>
+      </c>
+      <c r="B21" t="s">
+        <v>57</v>
+      </c>
+      <c r="C21" t="s">
+        <v>51</v>
+      </c>
+      <c r="D21" t="b">
+        <v>1</v>
+      </c>
+      <c r="E21" t="b">
+        <v>1</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="G21" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="H21" t="b">
+        <v>1</v>
+      </c>
+      <c r="I21" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="J21" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="K21" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="L21" s="6" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="D22" s="19" t="s">
+        <v>76</v>
+      </c>
+      <c r="E22" s="19" t="s">
+        <v>76</v>
+      </c>
+      <c r="F22" s="19" t="s">
+        <v>77</v>
+      </c>
+      <c r="G22" s="19" t="s">
+        <v>77</v>
+      </c>
+      <c r="H22" s="19" t="s">
+        <v>76</v>
+      </c>
+      <c r="I22" s="19" t="s">
+        <v>78</v>
+      </c>
+      <c r="J22" s="19" t="s">
+        <v>79</v>
+      </c>
+      <c r="K22" s="19" t="s">
+        <v>79</v>
+      </c>
+      <c r="L22" s="19" t="s">
+        <v>80</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="15">
+    <mergeCell ref="O15:O16"/>
+    <mergeCell ref="P15:P16"/>
+    <mergeCell ref="O2:P2"/>
+    <mergeCell ref="O9:O10"/>
+    <mergeCell ref="P9:P10"/>
+    <mergeCell ref="O11:O12"/>
+    <mergeCell ref="P11:P12"/>
+    <mergeCell ref="O13:O14"/>
+    <mergeCell ref="P13:P14"/>
+    <mergeCell ref="O3:O4"/>
+    <mergeCell ref="P3:P4"/>
+    <mergeCell ref="O5:O6"/>
+    <mergeCell ref="P5:P6"/>
+    <mergeCell ref="O7:O8"/>
+    <mergeCell ref="P7:P8"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <ignoredErrors>
+    <ignoredError sqref="F22:G22 L22" twoDigitTextYear="1"/>
+  </ignoredErrors>
+</worksheet>
 </file>
--- a/research/results/121225/summary_eval.xlsx
+++ b/research/results/121225/summary_eval.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Harshit Nigam\Desktop\Coding\Table Diversification\research\results\121225\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B33E7FC5-DA36-450C-B6C0-E26757B020C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1724C043-94BD-4DC4-9FDD-956E0424899B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="82">
   <si>
     <t>query_index</t>
   </si>
@@ -264,6 +264,9 @@
   </si>
   <si>
     <t>9/20</t>
+  </si>
+  <si>
+    <t>Success Rate:</t>
   </si>
 </sst>
 </file>
@@ -369,7 +372,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -378,23 +381,17 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -406,10 +403,15 @@
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1523,13 +1525,13 @@
   <dimension ref="A1:P22"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="5" max="5" width="9.5703125" customWidth="1"/>
-    <col min="6" max="6" width="9.85546875" customWidth="1"/>
+    <col min="5" max="5" width="10" customWidth="1"/>
+    <col min="6" max="6" width="10.42578125" customWidth="1"/>
     <col min="7" max="7" width="9.5703125" customWidth="1"/>
     <col min="8" max="8" width="10" customWidth="1"/>
-    <col min="9" max="9" width="10.5703125" customWidth="1"/>
-    <col min="10" max="11" width="11.140625" customWidth="1"/>
-    <col min="12" max="12" width="10.85546875" customWidth="1"/>
+    <col min="9" max="10" width="10.5703125" customWidth="1"/>
+    <col min="11" max="11" width="10.7109375" customWidth="1"/>
+    <col min="12" max="12" width="10.5703125" customWidth="1"/>
     <col min="15" max="15" width="10.42578125" customWidth="1"/>
     <col min="16" max="16" width="23" customWidth="1"/>
   </cols>
@@ -1600,7 +1602,7 @@
       <c r="I2" t="b">
         <v>1</v>
       </c>
-      <c r="J2" s="7" t="s">
+      <c r="J2" s="6" t="s">
         <v>62</v>
       </c>
       <c r="K2" t="b">
@@ -1609,10 +1611,10 @@
       <c r="L2" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="O2" s="10" t="s">
+      <c r="O2" s="12" t="s">
         <v>74</v>
       </c>
-      <c r="P2" s="10"/>
+      <c r="P2" s="12"/>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
@@ -1651,8 +1653,8 @@
       <c r="L3" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="O3" s="11"/>
-      <c r="P3" s="12" t="s">
+      <c r="O3" s="16"/>
+      <c r="P3" s="11" t="s">
         <v>68</v>
       </c>
     </row>
@@ -1681,7 +1683,7 @@
       <c r="H4" t="b">
         <v>1</v>
       </c>
-      <c r="I4" s="9" t="s">
+      <c r="I4" s="8" t="s">
         <v>67</v>
       </c>
       <c r="J4" t="b">
@@ -1693,8 +1695,8 @@
       <c r="L4" t="b">
         <v>1</v>
       </c>
-      <c r="O4" s="11"/>
-      <c r="P4" s="12"/>
+      <c r="O4" s="16"/>
+      <c r="P4" s="11"/>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
@@ -1730,11 +1732,11 @@
       <c r="K5" t="b">
         <v>1</v>
       </c>
-      <c r="L5" s="7" t="s">
+      <c r="L5" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="O5" s="13"/>
-      <c r="P5" s="12" t="s">
+      <c r="O5" s="17"/>
+      <c r="P5" s="11" t="s">
         <v>69</v>
       </c>
     </row>
@@ -1775,8 +1777,8 @@
       <c r="L6" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="O6" s="13"/>
-      <c r="P6" s="12"/>
+      <c r="O6" s="17"/>
+      <c r="P6" s="11"/>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
@@ -1812,11 +1814,11 @@
       <c r="K7" t="b">
         <v>1</v>
       </c>
-      <c r="L7" s="7" t="s">
+      <c r="L7" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="O7" s="14"/>
-      <c r="P7" s="12" t="s">
+      <c r="O7" s="18"/>
+      <c r="P7" s="11" t="s">
         <v>70</v>
       </c>
     </row>
@@ -1836,7 +1838,7 @@
       <c r="E8" t="b">
         <v>1</v>
       </c>
-      <c r="F8" s="6" t="b">
+      <c r="F8" t="b">
         <v>1</v>
       </c>
       <c r="G8" s="5" t="s">
@@ -1857,8 +1859,8 @@
       <c r="L8" t="b">
         <v>1</v>
       </c>
-      <c r="O8" s="14"/>
-      <c r="P8" s="12"/>
+      <c r="O8" s="18"/>
+      <c r="P8" s="11"/>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
@@ -1897,8 +1899,8 @@
       <c r="L9" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="O9" s="15"/>
-      <c r="P9" s="12" t="s">
+      <c r="O9" s="13"/>
+      <c r="P9" s="11" t="s">
         <v>75</v>
       </c>
     </row>
@@ -1918,29 +1920,29 @@
       <c r="E10" t="b">
         <v>1</v>
       </c>
-      <c r="F10" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="G10" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="H10" s="7" t="s">
+      <c r="F10" t="b">
+        <v>1</v>
+      </c>
+      <c r="G10" t="b">
+        <v>1</v>
+      </c>
+      <c r="H10" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="I10" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="J10" s="7" t="s">
+      <c r="I10" t="b">
+        <v>1</v>
+      </c>
+      <c r="J10" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="K10" s="6" t="b">
+      <c r="K10" t="b">
         <v>1</v>
       </c>
       <c r="L10" t="b">
         <v>1</v>
       </c>
-      <c r="O10" s="15"/>
-      <c r="P10" s="12"/>
+      <c r="O10" s="13"/>
+      <c r="P10" s="11"/>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
@@ -1958,7 +1960,7 @@
       <c r="E11" t="b">
         <v>1</v>
       </c>
-      <c r="F11" s="6" t="b">
+      <c r="F11" t="b">
         <v>1</v>
       </c>
       <c r="G11" s="4" t="s">
@@ -1967,20 +1969,20 @@
       <c r="H11" t="b">
         <v>1</v>
       </c>
-      <c r="I11" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="J11" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="K11" s="6" t="b">
+      <c r="I11" t="b">
+        <v>1</v>
+      </c>
+      <c r="J11" t="b">
+        <v>1</v>
+      </c>
+      <c r="K11" t="b">
         <v>1</v>
       </c>
       <c r="L11" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="O11" s="16"/>
-      <c r="P11" s="12" t="s">
+      <c r="O11" s="14"/>
+      <c r="P11" s="11" t="s">
         <v>71</v>
       </c>
     </row>
@@ -2000,29 +2002,29 @@
       <c r="E12" t="b">
         <v>1</v>
       </c>
-      <c r="F12" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="G12" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="H12" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="I12" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="J12" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="K12" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="L12" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="O12" s="16"/>
-      <c r="P12" s="12"/>
+      <c r="F12" t="b">
+        <v>1</v>
+      </c>
+      <c r="G12" t="b">
+        <v>1</v>
+      </c>
+      <c r="H12" t="b">
+        <v>1</v>
+      </c>
+      <c r="I12" t="b">
+        <v>1</v>
+      </c>
+      <c r="J12" t="b">
+        <v>1</v>
+      </c>
+      <c r="K12" t="b">
+        <v>1</v>
+      </c>
+      <c r="L12" t="b">
+        <v>1</v>
+      </c>
+      <c r="O12" s="14"/>
+      <c r="P12" s="11"/>
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
@@ -2040,43 +2042,43 @@
       <c r="E13" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="F13" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="G13" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="H13" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="I13" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="J13" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="K13" s="6" t="b">
+      <c r="F13" t="b">
+        <v>1</v>
+      </c>
+      <c r="G13" t="b">
+        <v>1</v>
+      </c>
+      <c r="H13" t="b">
+        <v>1</v>
+      </c>
+      <c r="I13" t="b">
+        <v>1</v>
+      </c>
+      <c r="J13" t="b">
+        <v>1</v>
+      </c>
+      <c r="K13" t="b">
         <v>1</v>
       </c>
       <c r="L13" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="O13" s="17"/>
-      <c r="P13" s="12" t="s">
+      <c r="O13" s="15"/>
+      <c r="P13" s="11" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
+      <c r="A14" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B14" s="7" t="s">
         <v>41</v>
       </c>
       <c r="C14" t="s">
         <v>37</v>
       </c>
-      <c r="D14" s="8" t="b">
+      <c r="D14" s="7" t="b">
         <v>0</v>
       </c>
       <c r="E14" s="2" t="s">
@@ -2103,8 +2105,8 @@
       <c r="L14" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="O14" s="17"/>
-      <c r="P14" s="12"/>
+      <c r="O14" s="15"/>
+      <c r="P14" s="11"/>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
@@ -2125,26 +2127,26 @@
       <c r="F15" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="G15" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="H15" s="7" t="s">
+      <c r="G15" t="b">
+        <v>1</v>
+      </c>
+      <c r="H15" s="6" t="s">
         <v>62</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="J15" s="7" t="s">
+      <c r="J15" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="K15" s="6" t="b">
+      <c r="K15" t="b">
         <v>1</v>
       </c>
       <c r="L15" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="O15" s="18"/>
-      <c r="P15" s="12" t="s">
+      <c r="O15" s="10"/>
+      <c r="P15" s="11" t="s">
         <v>73</v>
       </c>
     </row>
@@ -2164,29 +2166,29 @@
       <c r="E16" t="b">
         <v>1</v>
       </c>
-      <c r="F16" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="G16" s="6" t="b">
+      <c r="F16" t="b">
+        <v>1</v>
+      </c>
+      <c r="G16" t="b">
         <v>1</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="I16" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="J16" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="K16" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="L16" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="O16" s="18"/>
-      <c r="P16" s="12"/>
+      <c r="I16" t="b">
+        <v>1</v>
+      </c>
+      <c r="J16" t="b">
+        <v>1</v>
+      </c>
+      <c r="K16" t="b">
+        <v>1</v>
+      </c>
+      <c r="L16" t="b">
+        <v>1</v>
+      </c>
+      <c r="O16" s="10"/>
+      <c r="P16" s="11"/>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
@@ -2204,7 +2206,7 @@
       <c r="E17" t="b">
         <v>1</v>
       </c>
-      <c r="F17" s="6" t="b">
+      <c r="F17" t="b">
         <v>1</v>
       </c>
       <c r="G17" s="4" t="s">
@@ -2213,10 +2215,10 @@
       <c r="H17" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="I17" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="J17" s="6" t="b">
+      <c r="I17" t="b">
+        <v>1</v>
+      </c>
+      <c r="J17" t="b">
         <v>1</v>
       </c>
       <c r="K17" s="4" t="s">
@@ -2245,7 +2247,7 @@
       <c r="F18" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="G18" s="6" t="b">
+      <c r="G18" t="b">
         <v>1</v>
       </c>
       <c r="H18" t="b">
@@ -2254,7 +2256,7 @@
       <c r="I18" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="J18" s="6" t="b">
+      <c r="J18" t="b">
         <v>1</v>
       </c>
       <c r="K18" s="4" t="s">
@@ -2283,22 +2285,22 @@
       <c r="F19" t="b">
         <v>1</v>
       </c>
-      <c r="G19" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="H19" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="I19" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="J19" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="K19" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="L19" s="6" t="b">
+      <c r="G19" t="b">
+        <v>1</v>
+      </c>
+      <c r="H19" t="b">
+        <v>1</v>
+      </c>
+      <c r="I19" t="b">
+        <v>1</v>
+      </c>
+      <c r="J19" t="b">
+        <v>1</v>
+      </c>
+      <c r="K19" t="b">
+        <v>1</v>
+      </c>
+      <c r="L19" t="b">
         <v>1</v>
       </c>
     </row>
@@ -2321,22 +2323,22 @@
       <c r="F20" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="G20" s="6" t="b">
+      <c r="G20" t="b">
         <v>1</v>
       </c>
       <c r="H20" t="b">
         <v>1</v>
       </c>
-      <c r="I20" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="J20" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="K20" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="L20" s="6" t="b">
+      <c r="I20" t="b">
+        <v>1</v>
+      </c>
+      <c r="J20" t="b">
+        <v>1</v>
+      </c>
+      <c r="K20" t="b">
+        <v>1</v>
+      </c>
+      <c r="L20" t="b">
         <v>1</v>
       </c>
     </row>
@@ -2359,13 +2361,13 @@
       <c r="F21" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="G21" s="6" t="b">
+      <c r="G21" t="b">
         <v>1</v>
       </c>
       <c r="H21" t="b">
         <v>1</v>
       </c>
-      <c r="I21" s="6" t="b">
+      <c r="I21" t="b">
         <v>1</v>
       </c>
       <c r="J21" s="2" t="s">
@@ -2374,41 +2376,46 @@
       <c r="K21" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="L21" s="6" t="b">
+      <c r="L21" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="D22" s="19" t="s">
+      <c r="B22" s="12" t="s">
+        <v>81</v>
+      </c>
+      <c r="C22" s="12"/>
+      <c r="D22" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="E22" s="19" t="s">
+      <c r="E22" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="F22" s="19" t="s">
+      <c r="F22" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="G22" s="19" t="s">
+      <c r="G22" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="H22" s="19" t="s">
+      <c r="H22" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="I22" s="19" t="s">
+      <c r="I22" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="J22" s="19" t="s">
+      <c r="J22" s="9" t="s">
         <v>79</v>
       </c>
-      <c r="K22" s="19" t="s">
+      <c r="K22" s="9" t="s">
         <v>79</v>
       </c>
-      <c r="L22" s="19" t="s">
+      <c r="L22" s="9" t="s">
         <v>80</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="15">
+  <mergeCells count="16">
+    <mergeCell ref="B22:C22"/>
     <mergeCell ref="O15:O16"/>
     <mergeCell ref="P15:P16"/>
     <mergeCell ref="O2:P2"/>
